--- a/docs/collections/matsunami/metadata/data.xlsx
+++ b/docs/collections/matsunami/metadata/data.xlsx
@@ -661,7 +661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 1</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>b386852a-001d-1a10-2d8d-6e41134837d6</t>
+          <t>3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b386852a-001d-1a10-2d8d-6e41134837d6.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043.json</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>b386852a-001d-1a10-2d8d-6e41134837d6</t>
+          <t>3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/b386852a-001d-1a10-2d8d-6e41134837d6</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/494e59182b669ad941c19c079c3f02107d800b0e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5f8e3b73a877c1b436c3b641917835b2319f56b9.jpg</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22372</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22392</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -735,7 +735,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b386852a-001d-1a10-2d8d-6e41134837d6/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043/manifest</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -743,13 +743,13 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 2</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
+          <t>cb2ec445-a687-31d5-2490-595b266f2e9f</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cb2ec445-a687-31d5-2490-595b266f2e9f.json</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
+          <t>cb2ec445-a687-31d5-2490-595b266f2e9f</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cb2ec445-a687-31d5-2490-595b266f2e9f</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/15234e8804485f097183c3f745467e6d0e471c49.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/852a78418a9a04bf1b92c067d986e82d3ec79f3f.jpg</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22373</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22393</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cb2ec445-a687-31d5-2490-595b266f2e9f/manifest</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -831,13 +831,13 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 3</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16be420b-82b3-90c7-50f8-799342e29cdc</t>
+          <t>1450ac02-62c8-09df-7094-659562592168</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/16be420b-82b3-90c7-50f8-799342e29cdc.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1450ac02-62c8-09df-7094-659562592168.json</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16be420b-82b3-90c7-50f8-799342e29cdc</t>
+          <t>1450ac02-62c8-09df-7094-659562592168</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/16be420b-82b3-90c7-50f8-799342e29cdc</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/1450ac02-62c8-09df-7094-659562592168</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe2d93c2c97bc0f0077ce7a7a0c307c94a5f81bf.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2462895ef5c7d9bdc45e18bb5bb9d7fbcab8e78e.jpg</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22374</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22394</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/16be420b-82b3-90c7-50f8-799342e29cdc/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1450ac02-62c8-09df-7094-659562592168/manifest</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -919,13 +919,13 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 4</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08d8d249-a40a-6830-9929-541e6b3d5bae</t>
+          <t>65d62099-8834-2188-459e-b743d35d441c</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08d8d249-a40a-6830-9929-541e6b3d5bae.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/65d62099-8834-2188-459e-b743d35d441c.json</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>08d8d249-a40a-6830-9929-541e6b3d5bae</t>
+          <t>65d62099-8834-2188-459e-b743d35d441c</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/08d8d249-a40a-6830-9929-541e6b3d5bae</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/65d62099-8834-2188-459e-b743d35d441c</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1af3267d6d3cbd2d369df5646aedb706b6548957.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd368e63109056901adf5384c5e2bdcaa1607f4.jpg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22375</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22395</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -999,7 +999,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08d8d249-a40a-6830-9929-541e6b3d5bae/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/65d62099-8834-2188-459e-b743d35d441c/manifest</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1007,13 +1007,13 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 5</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9c523a30-8a11-8282-8660-5414684f3994</t>
+          <t>f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9c523a30-8a11-8282-8660-5414684f3994.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f9ade4bd-7e77-22da-0fb2-6e9a70396039.json</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9c523a30-8a11-8282-8660-5414684f3994</t>
+          <t>f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/9c523a30-8a11-8282-8660-5414684f3994</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c18a71926fa4972da76a335b32b10985f97e6173.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ce8485bdeab77a1158b245dea8c55315ab51c482.jpg</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22376</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22396</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9c523a30-8a11-8282-8660-5414684f3994/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f9ade4bd-7e77-22da-0fb2-6e9a70396039/manifest</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1095,13 +1095,13 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 6</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>460019c8-03da-63c8-a787-4132e04e7ac5</t>
+          <t>cce29331-33c5-a4c7-29af-415732362311</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/460019c8-03da-63c8-a787-4132e04e7ac5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cce29331-33c5-a4c7-29af-415732362311.json</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>460019c8-03da-63c8-a787-4132e04e7ac5</t>
+          <t>cce29331-33c5-a4c7-29af-415732362311</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/460019c8-03da-63c8-a787-4132e04e7ac5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cce29331-33c5-a4c7-29af-415732362311</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9a069fd35c7cb8ed1376e27be28878cddd61f443.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaa91b73b9001ed106bd2a5c2f70904d6865205c.jpg</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22377</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22397</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/460019c8-03da-63c8-a787-4132e04e7ac5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cce29331-33c5-a4c7-29af-415732362311/manifest</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 7</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,17 +1214,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4f41ecb4-3533-022d-a426-6120a11d3c04</t>
+          <t>cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4f41ecb4-3533-022d-a426-6120a11d3c04.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf6c9b5d-317d-2015-19b5-7f4b39ae7489.json</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4f41ecb4-3533-022d-a426-6120a11d3c04</t>
+          <t>cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/4f41ecb4-3533-022d-a426-6120a11d3c04</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/29056749d4692eda883fccae5d25802dd5bfc2ee.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/990b8ddb156670a9daf4e8f7e6f97104ba44b791.jpg</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22378</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22398</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1263,7 +1263,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4f41ecb4-3533-022d-a426-6120a11d3c04/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf6c9b5d-317d-2015-19b5-7f4b39ae7489/manifest</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1271,13 +1271,13 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 8</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
+          <t>8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5b1fae2a-0a39-1a00-0b88-9344abe54dc4.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cad3716-19aa-1ffb-6f88-b525a0a86c0d.json</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
+          <t>8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8d1430ac2119ff62b1dc4cca06bc3956076f1d6c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/919843b81a3503133efc5f095c1bec7f7d2d092d.jpg</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22379</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22399</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5b1fae2a-0a39-1a00-0b88-9344abe54dc4/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cad3716-19aa-1ffb-6f88-b525a0a86c0d/manifest</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 9</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7617ec5c-0126-9d91-3745-111d66c00c97</t>
+          <t>fdc773de-55e2-2aba-2d07-21439d12781e</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7617ec5c-0126-9d91-3745-111d66c00c97.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdc773de-55e2-2aba-2d07-21439d12781e.json</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7617ec5c-0126-9d91-3745-111d66c00c97</t>
+          <t>fdc773de-55e2-2aba-2d07-21439d12781e</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/7617ec5c-0126-9d91-3745-111d66c00c97</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/fdc773de-55e2-2aba-2d07-21439d12781e</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/117797ecf8307ad2c0e93c4a391e111e692e4c25.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5d32709520d42272a57362e0bc32613e92a8e2fe.jpg</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22380</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22400</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7617ec5c-0126-9d91-3745-111d66c00c97/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdc773de-55e2-2aba-2d07-21439d12781e/manifest</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1447,13 +1447,13 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 10</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1478,17 +1478,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>93c27fe3-5323-35dd-a352-557e157b2fe4</t>
+          <t>26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93c27fe3-5323-35dd-a352-557e157b2fe4.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/26bbe9de-1d48-8907-6a86-a98cb7379a79.json</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>93c27fe3-5323-35dd-a352-557e157b2fe4</t>
+          <t>26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/93c27fe3-5323-35dd-a352-557e157b2fe4</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/076c094e446ef86bf17581d7f86fdcd5e971587c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e22783edbe53bbcb3041e529263548a27f27ec62.jpg</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22381</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22401</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93c27fe3-5323-35dd-a352-557e157b2fe4/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/26bbe9de-1d48-8907-6a86-a98cb7379a79/manifest</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1535,13 +1535,13 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 11</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>cde28e92-19fd-1773-0532-cf58709e49f3</t>
+          <t>bc44a3f5-1eef-a511-3449-df32a2464223</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cde28e92-19fd-1773-0532-cf58709e49f3.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bc44a3f5-1eef-a511-3449-df32a2464223.json</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>cde28e92-19fd-1773-0532-cf58709e49f3</t>
+          <t>bc44a3f5-1eef-a511-3449-df32a2464223</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cde28e92-19fd-1773-0532-cf58709e49f3</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/bc44a3f5-1eef-a511-3449-df32a2464223</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2fcb14df3742dcb9b8678142cd31d99ce6dcb6e3.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0034c09167a6e0ac2133a8c9287c74d3f5eba0ee.jpg</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22382</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22402</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cde28e92-19fd-1773-0532-cf58709e49f3/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bc44a3f5-1eef-a511-3449-df32a2464223/manifest</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1623,13 +1623,13 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 12</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09c5b887-6418-673f-1252-392a47e61313</t>
+          <t>0585a340-5f5d-7697-099d-80c46b9a82ea</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/09c5b887-6418-673f-1252-392a47e61313.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0585a340-5f5d-7697-099d-80c46b9a82ea.json</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>09c5b887-6418-673f-1252-392a47e61313</t>
+          <t>0585a340-5f5d-7697-099d-80c46b9a82ea</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/09c5b887-6418-673f-1252-392a47e61313</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/0585a340-5f5d-7697-099d-80c46b9a82ea</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8114523c8ac71b949162a553176ed0122e91b693.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3e4954234102e3e5c0b4792381e46c7a3584b511.jpg</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22383</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22403</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/09c5b887-6418-673f-1252-392a47e61313/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0585a340-5f5d-7697-099d-80c46b9a82ea/manifest</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1711,13 +1711,13 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 13</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
+          <t>2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff0a9ad1-7c01-3010-3030-8f5b41e06021.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2dc15943-4526-6d80-39c4-f9cd7e2f93fd.json</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
+          <t>2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/29b79505258c493119d5baa4cb45ac5901edfcb1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9934df592cacdf12f1e9c54818c3045a2a706e8b.jpg</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22384</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22404</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff0a9ad1-7c01-3010-3030-8f5b41e06021/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2dc15943-4526-6d80-39c4-f9cd7e2f93fd/manifest</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 14</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
+          <t>a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/58031ba7-9fd4-9671-7631-081e8b3ca23f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a84c4e8e-0b23-5a85-1388-2601789f36ef.json</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
+          <t>a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe2fc105fd3d1fd823865a3ea490c9c024593bba.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ef9882f0fb65407123b59738a00fb72b5e55ed9d.jpg</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22385</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22405</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/58031ba7-9fd4-9671-7631-081e8b3ca23f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a84c4e8e-0b23-5a85-1388-2601789f36ef/manifest</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 15</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ae7ece32-793f-4769-3b24-a58812766775</t>
+          <t>ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae7ece32-793f-4769-3b24-a58812766775.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ab2b0ed4-03c0-1273-39ac-da2b659062e5.json</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ae7ece32-793f-4769-3b24-a58812766775</t>
+          <t>ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ae7ece32-793f-4769-3b24-a58812766775</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a7c0bfc49ff5ed85ea407c5067d909e2282d2ec9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a26dd714c8f1a590294958f729380ba7139162d2.jpg</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22386</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22406</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae7ece32-793f-4769-3b24-a58812766775/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ab2b0ed4-03c0-1273-39ac-da2b659062e5/manifest</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1975,13 +1975,13 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 16</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
+          <t>b386852a-001d-1a10-2d8d-6e41134837d6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bd1a48a6-1085-6c78-6887-e68a87da97e0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b386852a-001d-1a10-2d8d-6e41134837d6.json</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
+          <t>b386852a-001d-1a10-2d8d-6e41134837d6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/b386852a-001d-1a10-2d8d-6e41134837d6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5e2a1c2eb898ca236220cf4156c0a24ca67c62c8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/494e59182b669ad941c19c079c3f02107d800b0e.jpg</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22387</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22372</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bd1a48a6-1085-6c78-6887-e68a87da97e0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b386852a-001d-1a10-2d8d-6e41134837d6/manifest</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 17</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
+          <t>9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6f9fc8c8-8c9d-947d-2870-ba8c10d58208.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59.json</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
+          <t>9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/47e6436da5cd75b00ba56265e78478aefd871562.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/15234e8804485f097183c3f745467e6d0e471c49.jpg</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22388</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22373</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2143,7 +2143,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6f9fc8c8-8c9d-947d-2870-ba8c10d58208/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9edcc925-2fc6-4c72-8be3-6e2fc1b91b59/manifest</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2151,13 +2151,13 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 18</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>417a648b-2f60-3ead-8008-b3da070b94e6</t>
+          <t>16be420b-82b3-90c7-50f8-799342e29cdc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/417a648b-2f60-3ead-8008-b3da070b94e6.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/16be420b-82b3-90c7-50f8-799342e29cdc.json</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>417a648b-2f60-3ead-8008-b3da070b94e6</t>
+          <t>16be420b-82b3-90c7-50f8-799342e29cdc</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/417a648b-2f60-3ead-8008-b3da070b94e6</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/16be420b-82b3-90c7-50f8-799342e29cdc</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b6981673a0f2eebd03a6d3689ad66aac5cda140.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe2d93c2c97bc0f0077ce7a7a0c307c94a5f81bf.jpg</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22389</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22374</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/417a648b-2f60-3ead-8008-b3da070b94e6/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/16be420b-82b3-90c7-50f8-799342e29cdc/manifest</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2239,13 +2239,13 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 19</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>611110aa-6201-896f-4de4-efe045bd742d</t>
+          <t>08d8d249-a40a-6830-9929-541e6b3d5bae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/611110aa-6201-896f-4de4-efe045bd742d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08d8d249-a40a-6830-9929-541e6b3d5bae.json</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>611110aa-6201-896f-4de4-efe045bd742d</t>
+          <t>08d8d249-a40a-6830-9929-541e6b3d5bae</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/611110aa-6201-896f-4de4-efe045bd742d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/08d8d249-a40a-6830-9929-541e6b3d5bae</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/72770c5ac97a8cc689716954378bc898d5628475.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1af3267d6d3cbd2d369df5646aedb706b6548957.jpg</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22390</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22375</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/611110aa-6201-896f-4de4-efe045bd742d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08d8d249-a40a-6830-9929-541e6b3d5bae/manifest</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 20</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>856eac73-3f9a-a523-097e-b8e2d94c1748</t>
+          <t>9c523a30-8a11-8282-8660-5414684f3994</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/856eac73-3f9a-a523-097e-b8e2d94c1748.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9c523a30-8a11-8282-8660-5414684f3994.json</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>856eac73-3f9a-a523-097e-b8e2d94c1748</t>
+          <t>9c523a30-8a11-8282-8660-5414684f3994</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/856eac73-3f9a-a523-097e-b8e2d94c1748</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/9c523a30-8a11-8282-8660-5414684f3994</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4bb7694853f16a0621f20f9486bac3b80a6c12d9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c18a71926fa4972da76a335b32b10985f97e6173.jpg</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22391</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22376</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/856eac73-3f9a-a523-097e-b8e2d94c1748/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9c523a30-8a11-8282-8660-5414684f3994/manifest</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2415,13 +2415,13 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 21</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
+          <t>460019c8-03da-63c8-a787-4132e04e7ac5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/460019c8-03da-63c8-a787-4132e04e7ac5.json</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
+          <t>460019c8-03da-63c8-a787-4132e04e7ac5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/460019c8-03da-63c8-a787-4132e04e7ac5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5f8e3b73a877c1b436c3b641917835b2319f56b9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9a069fd35c7cb8ed1376e27be28878cddd61f443.jpg</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22392</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22377</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3d9eab09-8d3d-7a2d-a2a9-73e0c4209043/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/460019c8-03da-63c8-a787-4132e04e7ac5/manifest</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 22</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>cb2ec445-a687-31d5-2490-595b266f2e9f</t>
+          <t>4f41ecb4-3533-022d-a426-6120a11d3c04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cb2ec445-a687-31d5-2490-595b266f2e9f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4f41ecb4-3533-022d-a426-6120a11d3c04.json</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>cb2ec445-a687-31d5-2490-595b266f2e9f</t>
+          <t>4f41ecb4-3533-022d-a426-6120a11d3c04</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cb2ec445-a687-31d5-2490-595b266f2e9f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/4f41ecb4-3533-022d-a426-6120a11d3c04</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/852a78418a9a04bf1b92c067d986e82d3ec79f3f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/29056749d4692eda883fccae5d25802dd5bfc2ee.jpg</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22393</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22378</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cb2ec445-a687-31d5-2490-595b266f2e9f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4f41ecb4-3533-022d-a426-6120a11d3c04/manifest</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2591,13 +2591,13 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 23</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1450ac02-62c8-09df-7094-659562592168</t>
+          <t>5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1450ac02-62c8-09df-7094-659562592168.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5b1fae2a-0a39-1a00-0b88-9344abe54dc4.json</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1450ac02-62c8-09df-7094-659562592168</t>
+          <t>5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/1450ac02-62c8-09df-7094-659562592168</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/5b1fae2a-0a39-1a00-0b88-9344abe54dc4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2462895ef5c7d9bdc45e18bb5bb9d7fbcab8e78e.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8d1430ac2119ff62b1dc4cca06bc3956076f1d6c.jpg</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22394</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22379</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1450ac02-62c8-09df-7094-659562592168/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5b1fae2a-0a39-1a00-0b88-9344abe54dc4/manifest</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 24</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65d62099-8834-2188-459e-b743d35d441c</t>
+          <t>7617ec5c-0126-9d91-3745-111d66c00c97</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/65d62099-8834-2188-459e-b743d35d441c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7617ec5c-0126-9d91-3745-111d66c00c97.json</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>65d62099-8834-2188-459e-b743d35d441c</t>
+          <t>7617ec5c-0126-9d91-3745-111d66c00c97</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/65d62099-8834-2188-459e-b743d35d441c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/7617ec5c-0126-9d91-3745-111d66c00c97</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8fd368e63109056901adf5384c5e2bdcaa1607f4.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/117797ecf8307ad2c0e93c4a391e111e692e4c25.jpg</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22395</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22380</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/65d62099-8834-2188-459e-b743d35d441c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7617ec5c-0126-9d91-3745-111d66c00c97/manifest</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2767,13 +2767,13 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 25</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2798,17 +2798,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
+          <t>93c27fe3-5323-35dd-a352-557e157b2fe4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f9ade4bd-7e77-22da-0fb2-6e9a70396039.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/93c27fe3-5323-35dd-a352-557e157b2fe4.json</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
+          <t>93c27fe3-5323-35dd-a352-557e157b2fe4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/f9ade4bd-7e77-22da-0fb2-6e9a70396039</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/93c27fe3-5323-35dd-a352-557e157b2fe4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ce8485bdeab77a1158b245dea8c55315ab51c482.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/076c094e446ef86bf17581d7f86fdcd5e971587c.jpg</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22396</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22381</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f9ade4bd-7e77-22da-0fb2-6e9a70396039/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/93c27fe3-5323-35dd-a352-557e157b2fe4/manifest</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -2855,13 +2855,13 @@
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 26</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>cce29331-33c5-a4c7-29af-415732362311</t>
+          <t>cde28e92-19fd-1773-0532-cf58709e49f3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cce29331-33c5-a4c7-29af-415732362311.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cde28e92-19fd-1773-0532-cf58709e49f3.json</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>cce29331-33c5-a4c7-29af-415732362311</t>
+          <t>cde28e92-19fd-1773-0532-cf58709e49f3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cce29331-33c5-a4c7-29af-415732362311</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cde28e92-19fd-1773-0532-cf58709e49f3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aaa91b73b9001ed106bd2a5c2f70904d6865205c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2fcb14df3742dcb9b8678142cd31d99ce6dcb6e3.jpg</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22397</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22382</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cce29331-33c5-a4c7-29af-415732362311/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cde28e92-19fd-1773-0532-cf58709e49f3/manifest</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -2943,13 +2943,13 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 27</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
+          <t>09c5b887-6418-673f-1252-392a47e61313</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cf6c9b5d-317d-2015-19b5-7f4b39ae7489.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/09c5b887-6418-673f-1252-392a47e61313.json</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
+          <t>09c5b887-6418-673f-1252-392a47e61313</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/cf6c9b5d-317d-2015-19b5-7f4b39ae7489</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/09c5b887-6418-673f-1252-392a47e61313</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/990b8ddb156670a9daf4e8f7e6f97104ba44b791.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8114523c8ac71b949162a553176ed0122e91b693.jpg</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22398</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22383</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3023,7 +3023,7 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cf6c9b5d-317d-2015-19b5-7f4b39ae7489/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/09c5b887-6418-673f-1252-392a47e61313/manifest</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3031,13 +3031,13 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 28</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3062,17 +3062,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
+          <t>ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cad3716-19aa-1ffb-6f88-b525a0a86c0d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff0a9ad1-7c01-3010-3030-8f5b41e06021.json</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
+          <t>ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/8cad3716-19aa-1ffb-6f88-b525a0a86c0d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ff0a9ad1-7c01-3010-3030-8f5b41e06021</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/919843b81a3503133efc5f095c1bec7f7d2d092d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/29b79505258c493119d5baa4cb45ac5901edfcb1.jpg</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22399</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22384</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3111,7 +3111,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cad3716-19aa-1ffb-6f88-b525a0a86c0d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff0a9ad1-7c01-3010-3030-8f5b41e06021/manifest</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3119,13 +3119,13 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 29</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3150,17 +3150,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>fdc773de-55e2-2aba-2d07-21439d12781e</t>
+          <t>58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdc773de-55e2-2aba-2d07-21439d12781e.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/58031ba7-9fd4-9671-7631-081e8b3ca23f.json</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>fdc773de-55e2-2aba-2d07-21439d12781e</t>
+          <t>58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/fdc773de-55e2-2aba-2d07-21439d12781e</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/58031ba7-9fd4-9671-7631-081e8b3ca23f</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5d32709520d42272a57362e0bc32613e92a8e2fe.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fe2fc105fd3d1fd823865a3ea490c9c024593bba.jpg</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22400</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22385</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdc773de-55e2-2aba-2d07-21439d12781e/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/58031ba7-9fd4-9671-7631-081e8b3ca23f/manifest</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3207,13 +3207,13 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 30</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
+          <t>ae7ece32-793f-4769-3b24-a58812766775</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/26bbe9de-1d48-8907-6a86-a98cb7379a79.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae7ece32-793f-4769-3b24-a58812766775.json</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
+          <t>ae7ece32-793f-4769-3b24-a58812766775</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/26bbe9de-1d48-8907-6a86-a98cb7379a79</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ae7ece32-793f-4769-3b24-a58812766775</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e22783edbe53bbcb3041e529263548a27f27ec62.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a7c0bfc49ff5ed85ea407c5067d909e2282d2ec9.jpg</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22401</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22386</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3287,7 +3287,7 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/26bbe9de-1d48-8907-6a86-a98cb7379a79/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae7ece32-793f-4769-3b24-a58812766775/manifest</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3295,13 +3295,13 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 31</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>bc44a3f5-1eef-a511-3449-df32a2464223</t>
+          <t>bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bc44a3f5-1eef-a511-3449-df32a2464223.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bd1a48a6-1085-6c78-6887-e68a87da97e0.json</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>bc44a3f5-1eef-a511-3449-df32a2464223</t>
+          <t>bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/bc44a3f5-1eef-a511-3449-df32a2464223</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/bd1a48a6-1085-6c78-6887-e68a87da97e0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0034c09167a6e0ac2133a8c9287c74d3f5eba0ee.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5e2a1c2eb898ca236220cf4156c0a24ca67c62c8.jpg</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22402</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22387</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bc44a3f5-1eef-a511-3449-df32a2464223/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bd1a48a6-1085-6c78-6887-e68a87da97e0/manifest</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3383,13 +3383,13 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 32</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0585a340-5f5d-7697-099d-80c46b9a82ea</t>
+          <t>6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0585a340-5f5d-7697-099d-80c46b9a82ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6f9fc8c8-8c9d-947d-2870-ba8c10d58208.json</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0585a340-5f5d-7697-099d-80c46b9a82ea</t>
+          <t>6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/0585a340-5f5d-7697-099d-80c46b9a82ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/6f9fc8c8-8c9d-947d-2870-ba8c10d58208</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3e4954234102e3e5c0b4792381e46c7a3584b511.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/47e6436da5cd75b00ba56265e78478aefd871562.jpg</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22403</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22388</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0585a340-5f5d-7697-099d-80c46b9a82ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6f9fc8c8-8c9d-947d-2870-ba8c10d58208/manifest</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3471,13 +3471,13 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 33</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
+          <t>417a648b-2f60-3ead-8008-b3da070b94e6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2dc15943-4526-6d80-39c4-f9cd7e2f93fd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/417a648b-2f60-3ead-8008-b3da070b94e6.json</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
+          <t>417a648b-2f60-3ead-8008-b3da070b94e6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/2dc15943-4526-6d80-39c4-f9cd7e2f93fd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/417a648b-2f60-3ead-8008-b3da070b94e6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9934df592cacdf12f1e9c54818c3045a2a706e8b.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b6981673a0f2eebd03a6d3689ad66aac5cda140.jpg</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22404</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22389</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2dc15943-4526-6d80-39c4-f9cd7e2f93fd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/417a648b-2f60-3ead-8008-b3da070b94e6/manifest</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3559,13 +3559,13 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 34</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3590,17 +3590,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
+          <t>611110aa-6201-896f-4de4-efe045bd742d</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a84c4e8e-0b23-5a85-1388-2601789f36ef.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/611110aa-6201-896f-4de4-efe045bd742d.json</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
+          <t>611110aa-6201-896f-4de4-efe045bd742d</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/a84c4e8e-0b23-5a85-1388-2601789f36ef</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/611110aa-6201-896f-4de4-efe045bd742d</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ef9882f0fb65407123b59738a00fb72b5e55ed9d.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/72770c5ac97a8cc689716954378bc898d5628475.jpg</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22405</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22390</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3639,7 +3639,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a84c4e8e-0b23-5a85-1388-2601789f36ef/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/611110aa-6201-896f-4de4-efe045bd742d/manifest</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3647,13 +3647,13 @@
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 35</t>
+          <t>Catalogue of the Kawaguchi-Takakusu Collection of Sanskrit manuscripts. Note-book 20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
+          <t>856eac73-3f9a-a523-097e-b8e2d94c1748</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ab2b0ed4-03c0-1273-39ac-da2b659062e5.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/856eac73-3f9a-a523-097e-b8e2d94c1748.json</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
+          <t>856eac73-3f9a-a523-097e-b8e2d94c1748</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/ab2b0ed4-03c0-1273-39ac-da2b659062e5</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/matsunami/document/856eac73-3f9a-a523-097e-b8e2d94c1748</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a26dd714c8f1a590294958f729380ba7139162d2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4bb7694853f16a0621f20f9486bac3b80a6c12d9.jpg</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22406</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22391</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ab2b0ed4-03c0-1273-39ac-da2b659062e5/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/856eac73-3f9a-a523-097e-b8e2d94c1748/manifest</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3735,7 +3735,7 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
